--- a/base_prov_co/cruz_verde/cruz_verde_abbott_2026_10_13.xlsx
+++ b/base_prov_co/cruz_verde/cruz_verde_abbott_2026_10_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,65 +451,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoracion</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>url_imagen</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -536,15 +541,14 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -557,34 +561,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>53</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>135</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Encuentra Ensure Advance 850 g en Cruz Verde. Úsalo como apoyo nutricional o de bienestar según indicación, formato y datos del envase.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwa7ad7a7a/images/large/129816_5Ensure_Advance_Vainilla_Con_Proteina___HMB_Polvo_850g.jpg</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-con-proteina--hmb-polvo-850g/COCV_129816.html</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -611,15 +620,14 @@
           <t>7703186032157</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -632,34 +640,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>46</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>148</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Ensure Advance Lata x 850 g + Lata x 400 g disponible en Cruz Verde para rutinas de nutrición y bienestar. Compra online y confirma su presentación.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwcd1d9ad1/images/large/163576_1_Promo_Ensure_Advance_Lata_x_850g_Lata_x_400g.jpg</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/promo-ensure-advance-lata-x-850g--lata-x-400g/COCV_163576.html</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -686,15 +699,14 @@
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -707,34 +719,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>57</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>213</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw60dab794/images/large/402006_5Ensure_Advance_Vainilla_Con_Proteina___HMB_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-liquido-220-ml/COCV_402006.html</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -761,15 +778,14 @@
           <t>7703186033031</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -782,34 +798,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>71</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>145</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Encuentra Promo Ensure Advance Vainilla en Cruz Verde. Considera presentación, contenido, formato y recomendaciones del empaque antes de comprar.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwea077572/images/large/547197_1_PROMO_ENSURE_ADVANCE_PREC_ESP_CAJ_X_6FCOS_X_220ML_VAINILLA.jpg</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-con-proteina-liquido-220-ml-caja-por-6-unidades/COCV_547197.html</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -836,15 +857,14 @@
           <t>8427030008592</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -857,34 +877,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>53</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>153</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Ensure Advance Vainilla en Cruz Verde: considera presentación, sabor, formato, etapa y recomendaciones del empaque antes de comprar según disponibilidad.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw033080f8/images/large/111380_5Ensure_Advance_Vainilla_Con_Proteina___HMB_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-vainilla-con-proteina--hmb-polvo-400g/COCV_111380.html</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -911,15 +936,14 @@
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -932,34 +956,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>57</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>125</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Ensure Advance sabor fresa en formato líquido de 220 ml. Revisa contenido, porción e información nutricional antes de elegir.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwcaced56c/images/large/402008_5Ensure_Advance_Fresa_Con_Proteina___HMB_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-fresa-con-proteina--hmb-liquido-220-ml/COCV_402008.html</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -986,15 +1015,14 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1007,34 +1035,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>50</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>136</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Compra Ensure Fresa 850 g online en Cruz Verde. Considera formato, sabor y porción sugerida según la presentación del producto en línea.</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw8ca46b74/images/large/163112_5Ensure_Advance_Fresa_Con_Proteina___HMB_Polvo_850g.jpg</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-fresa-con-proteina--hmb-polvo-850g/COCV_163112.html</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1061,15 +1094,14 @@
           <t>8710428013873</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1082,34 +1114,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>50</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>213</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Ensure® Advance contiene HMB, proteína y 28 vitaminas y minerales incluyendo calcio y vitamina D. Ayuda a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw99cdb483/images/large/163111_3_Ensure_Advance_Fresa_Con_Proteina___HMB_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-fresa-polvo-400-gr/COCV_163111.html</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1136,15 +1173,14 @@
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1157,34 +1193,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>58</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>146</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Ensure Advance Chocolate Liquido 220 ml en Cruz Verde: considera formato, porción sugerida y recomendaciones del fabricante antes de incorporarlo.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwe3c35804/images/large/402007_5Ensure_Advance_Chocolate_Con_Proteina___HMB_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-chocolate-con-proteina--hmb-liquido-220-ml/COCV_402007.html</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1211,15 +1252,14 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1232,34 +1272,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>31</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>143</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Ensure Vainilla Polvo 400 g en Cruz Verde: considera presentación, sabor, cantidad y orientación profesional antes de incorporarlo a tu rutina.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw311c3983/images/large/109254_5Ensure_Base_Vainilla_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-base-vainilla-polvo-400g/COCV_109254.html</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1286,15 +1331,14 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1307,34 +1351,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>35</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>138</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Un vaso de Ensure® proporciona: 28 vitaminas y minerales esenciales, calcio y antioxidantes, vitamina D, omega-3 y es fuente de fibra FOS.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwd7b95be5/images/large/532007_5Ensure_Base_Vainilla_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-vainilla-liquido-220-ml/COCV_532007.html</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1361,15 +1410,14 @@
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1382,34 +1430,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>53</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>230</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Ensure® Advance es nutrición especializada para adultos con HMB, proteína y 28 vitaminas y minerales. Ideal para ayudar a recuperar la masa muscular perdida por una condición de salud, y a mejorar la vitalidad, fuerza y movilidad.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwfc33ec59/images/large/530022_5Ensure_Advance_Cafe_Con_Proteina___HMB_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-cafe-liquido-220-ml/COCV_530022.html</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1436,15 +1489,14 @@
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1457,34 +1509,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>49</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>55</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Ensure Advance Nutricion Especializada Tarro 400Gr Cafe</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw2b5231fd/images/large/578454_5Ensure_Advance_Cafe_Con_Proteina___HMB_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/ensure-advance-nutricion-especializada-tarro-400gr-cafe/COCV_578454.html</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1511,15 +1568,14 @@
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1532,34 +1588,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>50</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>136</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Glucerna 850 Gr 850 g disponible en Cruz Verde para rutinas de nutrición y bienestar. Compra online y confirma su presentación en línea.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw7dd3d0c2/images/large/577824_5Glucerna_Formula_para_Diabetes_Polvo_Vainilla_850g.jpg</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-tarro-x-850gr-vainilla/COCV_577824.html</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1586,15 +1647,14 @@
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1607,34 +1667,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>54</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>222</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwa7746763/images/large/128687_5Glucerna_Forrmula_para_Diabetes_Liquido_Vainilla_237_Ml.jpg</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-vainilla-liquido-220-ml/COCV_128687.html</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1661,15 +1726,14 @@
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1682,34 +1746,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>82</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>138</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Compra Glucerna por 1 Tarro por 850gr+ 1 400gr Vainilla online en Cruz Verde. Considera formato, sabor y porción sugerida antes de usarlo.</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw056bc6e5/images/large/572641_1_Promo_Glucerna_Descuento_Paquete_por_1_Tarro_por_850Gr_1_Tarro_por_400Gr_Vainilla.jpg</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/promo-glucerna-descuento-paquete-por-1-tarro-por-850gr-1-tarro-por-400gr-vainilla/COCV_572641.html</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1736,15 +1805,14 @@
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1757,34 +1825,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>52</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>155</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Glucerna Vainilla Liquido 220 ml en Cruz Verde: considera presentación, disponibilidad, información del empaque y orientación profesional antes de comprar.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw21866391/images/large/547912_1_PROMO_GLUCERNA_ABBOTT_PREC_ESPE_093KCAL_ML_CAJ_X_6BOT_X_237ML_VAINILLA.jpg</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-vainilla-liquido-220-ml-caja-x6-unidades/COCV_547912.html</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1811,15 +1884,14 @@
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1832,34 +1904,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>51</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>222</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>¡Controla tus niveles de azúcar! Glucerna® te ayuda a estabilizar tus niveles de azúcar desde el primer día gracias a su doble método de acción que permite mejorar la producción de insulina y reducir la resistencia a ella.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwa4a7b4c4/images/large/138288_3Glucerna_Formula_para_Diabetes_Liquido_Fresa_237_Ml.jpg</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-fresa-liquido-220-ml/COCV_138288.html</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1886,15 +1963,14 @@
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1907,34 +1983,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>50</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>154</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Glucerna Vainilla Polvo 400 g en Cruz Verde: considera presentación, formato, disponibilidad y datos del empaque antes de elegirlo. según tus necesidades.</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwd8a58e21/images/large/142214_5Glucerna_Formula_para_Diabetes_Polvo_Vainilla_400g.jpg</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/glucerna-vainilla-polvo-400-gr/COCV_142214.html</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1961,15 +2042,14 @@
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1982,34 +2062,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>24</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>105</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Referencia: 157457Registro Sanitario: RSA-0035011-2024Incluye 0% de impuestosPresentación: tarro x 400 gr</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://copservir.vtexassets.com/arquivos/ids/1942555/GLUCERNA-CAPUCHINO-POLVO_F.png?v=639167595673670000</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/glucerna-capuchino-polvo-157457/p</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2036,15 +2121,14 @@
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2057,34 +2141,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>46</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>147</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Compra Pedialyte Max 60 Uva 500 ml en Cruz Verde. Ten presente formato, presentación, disponibilidad e información del empaque antes de adquirirlo.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwdcff4817/images/large/96738_1_PEDIALYTE_CON_ZINC_60MEQNa_L_SOL_ORAL_FCO_X_500ML_UVA.jpg</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-uva-500-ml/COCV_96738.html</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2111,15 +2200,14 @@
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2132,34 +2220,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>61</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>139</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Pedialyte Max 60 sabor fresa de 500 ml, una presentación de suero pediátrico. Revisa concentración, sabor y disponibilidad antes de elegir.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw40d23db8/images/large/165575_1_PEDIALYTE_MAX_CON_ZINC_60MEQNA_L_SOL_ORAL_FCO_X_500ML_FRESA.jpg</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-fresa-500-ml/COCV_165575.html</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2186,15 +2279,14 @@
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2207,34 +2299,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>57</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>115</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Pedialyte Max 60 sabor manzana de 500 ml. Revisa esta presentación de suero oral 60 mEq, su sabor y disponibilidad.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw76a0427e/images/large/96736_1_PEDIALYTE_CON_ZINC_60MEQNa_L_SOL_ORAL_FCO_X_500ML_MANZANA.jpg</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-manzana-500-ml/COCV_96736.html</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2261,15 +2358,14 @@
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2282,34 +2378,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>47</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>151</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Suero De Rehidratacion Pedialyte Max 60 Coco 500 ml en Cruz Verde: considera formato, cantidad y condiciones indicadas en el empaque antes de elegirlo.</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwb30e022c/images/large/165574_1_PEDIALYTE_MAX_CON_ZINC_60MEQNA_L_SOL_ORAL_FCO_X_500ML_COCO.jpg</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-max-60-coco-500-ml/COCV_165574.html</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2336,15 +2437,14 @@
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2357,34 +2457,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>52</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>246</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Pedialyte® 30 mEq - 45 mEq está científicamente diseñado para prevenir la deshidratación leve y para hidratar de forma más rápida y efectiva, principalmente en casos de deshidratación por actividad física intensa o exposición prolongada al calor.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwefb18bd5/images/large/134768_1_PEDIALYTE_CON_ZINC_30MEQNa_L_SOL_ORAL_FCO_X_500ML_CEREZA.jpg</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-cereza-500-ml/COCV_134768.html</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2411,15 +2516,14 @@
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2432,34 +2536,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>51</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>246</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Pedialyte® 30 mEq - 45 mEq está científicamente diseñado para prevenir la deshidratación leve y para hidratar de forma más rápida y efectiva, principalmente en casos de deshidratación por actividad física intensa o exposición prolongada al calor.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwe2614e2a/images/large/96734_1_PEDIALYTE_CON_ZINC_45MEQNa_L_SOL_ORAL_FCO_X_500ML_FRESA.jpg</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-45-fresa-500-ml/COCV_96734.html</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2486,15 +2595,14 @@
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2507,34 +2615,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>50</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>246</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Pedialyte® 30 mEq - 45 mEq está científicamente diseñado para prevenir la deshidratación leve y para hidratar de forma más rápida y efectiva, principalmente en casos de deshidratación por actividad física intensa o exposición prolongada al calor.</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw23f80837/images/large/134770_1_PEDIALYTE_CON_ZINC_30MEQNa_L_SOL_ORAL_FCO_X_500ML_COCO.jpg</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-coco-500-ml/COCV_134770.html</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2561,15 +2674,14 @@
           <t>7501033959950</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2582,34 +2694,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>53</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>246</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Pedialyte® 30 mEq - 45 mEq está científicamente diseñado para prevenir la deshidratación leve y para hidratar de forma más rápida y efectiva, principalmente en casos de deshidratación por actividad física intensa o exposición prolongada al calor.</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw4053f574/images/large/134769_1_PEDIALYTE_CON_ZINC_30MEQNa_L_SOL_ORAL_FCO_X_500ML_MANZANA.jpg</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-manzana-500-ml/COCV_134769.html</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2636,15 +2753,14 @@
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2657,34 +2773,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>53</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>246</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Pedialyte® 30 mEq - 45 mEq está científicamente diseñado para prevenir la deshidratación leve y para hidratar de forma más rápida y efectiva, principalmente en casos de deshidratación por actividad física intensa o exposición prolongada al calor.</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwef87bc86/images/large/134771_1_PEDIALYTE_CON_ZINC_30MEQNa_L_SOL_ORAL_FCO_X_500ML_DURAZNO.jpg</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-30-durazno-500-ml/COCV_134771.html</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2711,15 +2832,14 @@
           <t>7501033962394</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2732,34 +2852,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>53</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>246</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Pedialyte® 30 mEq - 45 mEq está científicamente diseñado para prevenir la deshidratación leve y para hidratar de forma más rápida y efectiva, principalmente en casos de deshidratación por actividad física intensa o exposición prolongada al calor.</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw63e62bd0/images/large/394640_1_PEDIALYTE_ACTIVE_45MEQNa_L_SOL_ORAL_FCO_X_500ML_GUARANA.jpg</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/suero-de-rehidratacion-pedialyte-active-45-guarana-500-ml/COCV_394640.html</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2786,15 +2911,14 @@
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2807,34 +2931,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>4</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>52</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>40</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Pediasure Peptigro Tarro por 400Gr Fresa</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwb195808b/images/large/574284_4Pediasure_Formula_Nutricional_Fresa_Ninos_2_10_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-400gr-fresa/COCV_574284.html</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2861,15 +2990,14 @@
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2882,34 +3010,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>5</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>56</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>139</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Compra PediaSure 1600 1600 g online en Cruz Verde. Considera formato, sabor y porción sugerida según la presentación del producto en línea.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwc68020e2/images/large/556914_5Pediasure_Formula_Nutricional_Vainilla_Ninos_2_10_liquido_1600g.jpg</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-10kcalml-lata-x-1600gr-vainilla/COCV_556914.html</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2936,15 +3069,14 @@
           <t>8886451012043</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2957,34 +3089,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>5</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>55</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>156</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw3f32c42e/images/large/574305_5Pediasure_Formula_Nutricional_Vainilla_Ninos_2_10_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-400gr-vainilla/COCV_574305.html</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3011,15 +3148,14 @@
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3032,34 +3168,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>5</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>59</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>67</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Pediasure Vainilla para bienestar diario. Disponible en Cruz Verde.</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw511f56fc/images/large/525504_5Pediasure_Formula_Nutricional_Vainilla_Ninos_2_10_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-vainilla-liquido-220ml/COCV_525504.html</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3086,15 +3227,14 @@
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3107,34 +3247,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>5</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>56</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>156</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwb4d2a900/images/large/525503_5Pediasure_Formula_Nutricional_Fresa_Ninos_2_10_Liquido_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-fresa-liquido-220-ml/COCV_525503.html</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3161,15 +3306,14 @@
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3182,34 +3326,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>52</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>149</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Pediasure Peptigro Tarro por 850 g Fresa en Cruz Verde: considera presentación, sabor, formato, etapa y recomendaciones del empaque antes de comprar.</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw7d9ce4d3/images/large/574283_5Pediasure_Formula_Nutricional_Fresa_Ninos_2_10_Polvo_850g.jpg</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-850gr-fresa/COCV_574283.html</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3236,15 +3385,14 @@
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3257,34 +3405,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>4</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>52</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>40</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Pediasure Peptigro Tarro por 400Gr Fresa</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwb195808b/images/large/574284_4Pediasure_Formula_Nutricional_Fresa_Ninos_2_10_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-peptigro-tarro-por-400gr-fresa/COCV_574284.html</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3311,15 +3464,14 @@
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3332,34 +3484,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>65</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>156</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Para que tu hijo crezca es importante una adecuada alimentación, apóyalo con Pediasure® y su fórmula especializada, ¡ayúdalo a alcanzar su máximo potencial!</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwf0f87e56/images/large/547911_1PROMO_PEDIASURE_ABBOTT_PREC_ESPE_1.0_KCAL_ML_CAJ_X_6BOT_X_220ML_VAINILLA.jpg</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/promo-pediasure-abbott-precio-especial-10-kcal-ml-caja-x-6bot-x-220ml-vainilla/COCV_547911.html</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3386,15 +3543,14 @@
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3407,34 +3563,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>4</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>71</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>64</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Pediasure Nutricion Especializada 10+ Años Frasco 220Ml Vainilla</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwe7f28b28/images/large/578455_4Pediasure_Formula_Nutricional_para_Adolescentes_10__Vainilla_Polvo_220_Ml.jpg</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/pediasure-nutricion-especializada-10-anos-frasco-220ml-vainilla/COCV_578455.html</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3461,15 +3622,14 @@
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3482,34 +3642,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>3</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>33</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>137</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Encuentra Similac Etapa 1 1400 g en Cruz Verde. Úsalo como apoyo nutricional o de bienestar según indicación, formato y datos del envase.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw098060a4/images/large/547206_3Fomula_Infantil_Etapa_1_Similac_5HMOs_0_6M_Polvo_1400g.jpg</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-1-hmo-polvo-1400-gr/COCV_547206.html</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3536,15 +3701,14 @@
           <t>5099864017014</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3557,34 +3721,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>3</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>32</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>143</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Descubre Similac 2 5HMO: fórmula infantil en polvo de 800g, diseñada para apoyar el desarrollo de tu bebé. Compra ahora y asegura su nutrición.</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw7847c7b6/images/large/545921_3Fomula_Infantil_Etapa_2_Similac_5HMOs_6_12M_Polvo_800g.jpg</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-2-5hmo-polvo-800-gr/COCV_545921.html</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3611,15 +3780,14 @@
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3632,34 +3800,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>4</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>33</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>153</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Fórmula Infantil Similac 3 5HMO Polvo 1800 g en Cruz Verde: considera presentación, sabor, formato, etapa y recomendaciones del empaque antes de comprar.</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw890c1655/images/large/547215_4Fomula_Infantil_Etapa_3_Similac_5HMOs_12M_en_Adelante_Polvo_1800g.jpg</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-3-5hmo-polvo-1800gr/COCV_547215.html</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3686,15 +3859,14 @@
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3707,34 +3879,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>32</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>240</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Similac® 3 Kid es un alimento lácteo en polvo para niños desde los 2 años, con una fórmula científicamente diseñada que incluye grasas de fácil digestión, 5 HMOs (Oligosacáridos), nucleótidos, probiótico, prebióticos, DHA, hierro y luteína.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw3b2f0b48/images/large/547208_3Fomula_Infantil_Etapa_3_Similac_5HMOs_12M_en_Adelante_Polvo_800g_.jpg</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-3-5-hmos-kid-lata-x-800gr-vainilla/COCV_547208.html</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3761,15 +3938,14 @@
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3782,34 +3958,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>32</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>240</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Similac® 3 Kid es un alimento lácteo en polvo para niños desde los 2 años, con una fórmula científicamente diseñada que incluye grasas de fácil digestión, 5 HMOs (Oligosacáridos), nucleótidos, probiótico, prebióticos, DHA, hierro y luteína.</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw78f6bc87/images/large/546988_3Fomula_Infantil_Etapa_3_Similac_5HMOs_12M_en_Adelante_Polvo_350g.jpg</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-3-5-hmos-kid-lata-x-350gr-vainilla/COCV_546988.html</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3836,15 +4017,14 @@
           <t>8427030004938</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3857,34 +4037,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>3</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>45</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>33</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Similac Antireflujo Tarro X 375Gr</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dwa0aaf8e6/images/large/113960_3Fomula_Infantil_Especializada_Similac_Anti_Reflujo_0_12M_Polvo_375g.jpg</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-antireflujo-tarro-x-375gr/COCV_113960.html</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3911,15 +4096,14 @@
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3932,34 +4116,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>3</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>51</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>38</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Similac Neosure Iq Polvo Lata X 370 Gr</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw5cd89b21/images/large/100466_3Fomula_Infantil_Especializada_Similac_NeoSure_Prematuros_0_12M_Polvo_370g.jpg</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-neosure-polvo-370-gr/COCV_100466.html</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3986,15 +4175,14 @@
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4007,34 +4195,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>3</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>55</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>51</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Similac Arroz Hmo Lactantes 0-12 Meses Lata X 400Gr</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw58f83df2/images/large/544508_3Fomula_Infantil_Especializada_Similac_Rice_Proteina_de_Arroz_0_36M_Polvo_400g.jpg</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/similac-arroz-hmo-lactantes-0-12-meses-lata-x-400gr/COCV_544508.html</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4061,15 +4254,14 @@
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4082,34 +4274,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>3</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>54</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>49</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Similac Sensitive Sin Lactosa Polvo Tarro X 400Gr</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw11f08b7d/images/large/96845_3Fomula_Infantil_Especializada_Similac_Sensitive_Sin_Lactosa_0_12M_Polvo_375g_.jpg</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-sin-lactosa-polvo-375-gr/COCV_96845.html</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4136,15 +4333,14 @@
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4157,34 +4353,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
         <v>3</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>41</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>136</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Similac Total Comfort 1 1400 g disponible en Cruz Verde para rutinas de nutrición y bienestar. Compra online y confirma su presentación.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://beta1.cruzverde.com.co/on/demandware.static/-/Sites-masterCatalog_Colombia/default/dw001f8b38/images/large/146187_3Fomula_Infantil_Etapa_1_Similac_Total_Comfort_0_12M_Polvo_1400g.jpg</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>https://www.cruzverde.com.co/formula-infantil-similac-total-comfort-etapa-1-polvo-1400-gr/COCV_146187.html</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
